--- a/VerveStacks_BIH_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_BIH_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BIH_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6317B480-BF8D-4A39-B32A-4755E22A50E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9E687FEC-1D25-45DF-ADE2-2188B9176F90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -661,7 +661,7 @@
     <t>e_spv_BIH_001</t>
   </si>
   <si>
-    <t>solar resource in cluster 1</t>
+    <t>solar resource near Banja Luka (cluster 1)</t>
   </si>
   <si>
     <t>annual</t>
@@ -673,79 +673,79 @@
     <t>e_spv_BIH_002</t>
   </si>
   <si>
-    <t>solar resource in cluster 2</t>
+    <t>solar resource near Mostar (cluster 2)</t>
   </si>
   <si>
     <t>e_spv_BIH_003</t>
   </si>
   <si>
-    <t>solar resource in cluster 3</t>
+    <t>solar resource near Mostar (cluster 3)</t>
   </si>
   <si>
     <t>e_spv_BIH_004</t>
   </si>
   <si>
-    <t>solar resource in cluster 4</t>
+    <t>solar resource near Mostar (cluster 4)</t>
   </si>
   <si>
     <t>e_spv_BIH_005</t>
   </si>
   <si>
-    <t>solar resource in cluster 5</t>
+    <t>solar resource near Sarajevo (cluster 5)</t>
   </si>
   <si>
     <t>e_spv_BIH_006</t>
   </si>
   <si>
-    <t>solar resource in cluster 6</t>
+    <t>solar resource near Cazin (cluster 6)</t>
   </si>
   <si>
     <t>e_spv_BIH_007</t>
   </si>
   <si>
-    <t>solar resource in cluster 7</t>
+    <t>solar resource near Prijedor (cluster 7)</t>
   </si>
   <si>
     <t>e_spv_BIH_008</t>
   </si>
   <si>
-    <t>solar resource in cluster 8</t>
+    <t>solar resource near Banja Luka (cluster 8)</t>
   </si>
   <si>
     <t>e_spv_BIH_009</t>
   </si>
   <si>
-    <t>solar resource in cluster 9</t>
+    <t>solar resource near Prijedor (cluster 9)</t>
   </si>
   <si>
     <t>e_spv_BIH_010</t>
   </si>
   <si>
-    <t>solar resource in cluster 10</t>
+    <t>solar resource near Sarajevo (cluster 10)</t>
   </si>
   <si>
     <t>e_spv_BIH_011</t>
   </si>
   <si>
-    <t>solar resource in cluster 11</t>
+    <t>solar resource near Sarajevo (cluster 11)</t>
   </si>
   <si>
     <t>e_spv_BIH_012</t>
   </si>
   <si>
-    <t>solar resource in cluster 12</t>
+    <t>solar resource near Bijeljina (cluster 12)</t>
   </si>
   <si>
     <t>e_spv_BIH_013</t>
   </si>
   <si>
-    <t>solar resource in cluster 13</t>
+    <t>solar resource near Banja Luka (cluster 13)</t>
   </si>
   <si>
     <t>e_spv_BIH_014</t>
   </si>
   <si>
-    <t>solar resource in cluster 14</t>
+    <t>solar resource near Doboj (cluster 14)</t>
   </si>
   <si>
     <t>~fi_t</t>
@@ -808,34 +808,88 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_BIH_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BIH_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BIH_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BIH_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BIH_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BIH_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BIH_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BIH_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BIH_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BIH_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_BIH_012</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 12</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BIH_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BIH_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BIH_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
+    <t>distr_solelc_spv_BIH_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_BIH_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
   </si>
   <si>
     <t>distr_solelc_spv_BIH_011</t>
@@ -844,100 +898,88 @@
     <t>connecting solar to buses in cluster 11</t>
   </si>
   <si>
-    <t>distr_solelc_spv_BIH_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BIH_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BIH_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BIH_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BIH_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BIH_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BIH_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BIH_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_BIH_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
-    <t>e_BA17-220_BIH,e_BA9-220_BIH,e_Doboj_BIH,e_Bijeljina_BIH</t>
+    <t>e_Mostar_BIH,e_Trebinje_BIH</t>
+  </si>
+  <si>
+    <t>e_Mostar_BIH,e_SirokiBrijeg_BIH</t>
+  </si>
+  <si>
+    <t>e_Sarajevo_BIH</t>
   </si>
   <si>
     <t>e_Prijedor_BIH</t>
   </si>
   <si>
-    <t>e_SirokiBrijeg_BIH,e_w251735977-220_BIH</t>
+    <t>e_SirokiBrijeg_BIH,e_Travnik_BIH</t>
   </si>
   <si>
     <t>e_Prijedor_BIH,e_Doboj_BIH</t>
   </si>
   <si>
+    <t>e_Travnik_BIH,e_Prijedor_BIH,e_Sarajevo_BIH,e_Doboj_BIH</t>
+  </si>
+  <si>
+    <t>e_Mostar_BIH,e_Trebinje_BIH,e_Sarajevo_BIH</t>
+  </si>
+  <si>
+    <t>e_Sarajevo_BIH,e_Tuzla_BIH,e_Doboj_BIH,e_Bijeljina_BIH</t>
+  </si>
+  <si>
+    <t>e_Travnik_BIH,e_Mostar_BIH</t>
+  </si>
+  <si>
+    <t>e_Prijedor_BIH,e_Travnik_BIH</t>
+  </si>
+  <si>
     <t>e_Bratunac_BIH</t>
   </si>
   <si>
-    <t>e_w251735977-220_BIH,e_Mostar_BIH</t>
-  </si>
-  <si>
-    <t>e_Prijedor_BIH,e_w251735977-220_BIH</t>
-  </si>
-  <si>
-    <t>e_w251735977-220_BIH,e_Prijedor_BIH,e_BA17-220_BIH,e_Doboj_BIH</t>
-  </si>
-  <si>
-    <t>e_Mostar_BIH,e_Trebinje_BIH,e_BA17-220_BIH</t>
-  </si>
-  <si>
-    <t>e_Mostar_BIH,e_Trebinje_BIH</t>
-  </si>
-  <si>
-    <t>e_Mostar_BIH,e_SirokiBrijeg_BIH</t>
-  </si>
-  <si>
-    <t>e_BA17-220_BIH</t>
+    <t>distr_wonelc_won_BIH_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BIH_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BIH_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BIH_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BIH_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BIH_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_BIH_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
   </si>
   <si>
     <t>distr_wonelc_won_BIH_008</t>
@@ -946,18 +988,6 @@
     <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_wonelc_won_BIH_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BIH_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_BIH_010</t>
   </si>
   <si>
@@ -970,142 +1000,112 @@
     <t>connecting wind onshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wonelc_won_BIH_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BIH_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BIH_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BIH_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_BIH_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
+    <t>elc_won_BIH_001</t>
+  </si>
+  <si>
+    <t>e_Trebinje_BIH</t>
+  </si>
+  <si>
+    <t>elc_won_BIH_004</t>
+  </si>
+  <si>
+    <t>e_Mostar_BIH</t>
+  </si>
+  <si>
+    <t>elc_won_BIH_009</t>
+  </si>
+  <si>
+    <t>e_Mostar_BIH,e_Travnik_BIH</t>
+  </si>
+  <si>
+    <t>elc_won_BIH_005</t>
+  </si>
+  <si>
+    <t>e_Doboj_BIH</t>
+  </si>
+  <si>
+    <t>elc_won_BIH_002</t>
+  </si>
+  <si>
+    <t>elc_won_BIH_007</t>
+  </si>
+  <si>
+    <t>elc_won_BIH_006</t>
+  </si>
+  <si>
+    <t>e_Bijeljina_BIH</t>
   </si>
   <si>
     <t>elc_won_BIH_008</t>
   </si>
   <si>
-    <t>elc_won_BIH_006</t>
-  </si>
-  <si>
-    <t>e_Bijeljina_BIH</t>
-  </si>
-  <si>
-    <t>elc_won_BIH_005</t>
-  </si>
-  <si>
-    <t>e_Doboj_BIH</t>
-  </si>
-  <si>
     <t>elc_won_BIH_010</t>
   </si>
   <si>
-    <t>e_SirokiBrijeg_BIH</t>
+    <t>e_Travnik_BIH</t>
   </si>
   <si>
     <t>elc_won_BIH_003</t>
   </si>
   <si>
-    <t>e_Mostar_BIH</t>
-  </si>
-  <si>
-    <t>elc_won_BIH_009</t>
-  </si>
-  <si>
-    <t>e_SirokiBrijeg_BIH,e_Mostar_BIH,e_Zenica_BIH</t>
-  </si>
-  <si>
-    <t>elc_won_BIH_004</t>
-  </si>
-  <si>
-    <t>elc_won_BIH_001</t>
-  </si>
-  <si>
-    <t>e_Trebinje_BIH</t>
-  </si>
-  <si>
-    <t>elc_won_BIH_007</t>
-  </si>
-  <si>
-    <t>elc_won_BIH_002</t>
-  </si>
-  <si>
     <t>e_won_BIH_001</t>
   </si>
   <si>
-    <t>wind resource in cluster 1</t>
+    <t>wind onshore resource near Mostar (cluster 1)</t>
   </si>
   <si>
     <t>e_won_BIH_002</t>
   </si>
   <si>
-    <t>wind resource in cluster 2</t>
+    <t>wind onshore resource near Sarajevo (cluster 2)</t>
   </si>
   <si>
     <t>e_won_BIH_003</t>
   </si>
   <si>
-    <t>wind resource in cluster 3</t>
+    <t>wind onshore resource near Mostar (cluster 3)</t>
   </si>
   <si>
     <t>e_won_BIH_004</t>
   </si>
   <si>
-    <t>wind resource in cluster 4</t>
+    <t>wind onshore resource near Mostar (cluster 4)</t>
   </si>
   <si>
     <t>e_won_BIH_005</t>
   </si>
   <si>
-    <t>wind resource in cluster 5</t>
+    <t>wind onshore resource near Bijeljina (cluster 5)</t>
   </si>
   <si>
     <t>e_won_BIH_006</t>
   </si>
   <si>
-    <t>wind resource in cluster 6</t>
+    <t>wind onshore resource near Bijeljina (cluster 6)</t>
   </si>
   <si>
     <t>e_won_BIH_007</t>
   </si>
   <si>
-    <t>wind resource in cluster 7</t>
+    <t>wind onshore resource near Prijedor (cluster 7)</t>
   </si>
   <si>
     <t>e_won_BIH_008</t>
   </si>
   <si>
-    <t>wind resource in cluster 8</t>
+    <t>wind onshore resource near Prijedor (cluster 8)</t>
   </si>
   <si>
     <t>e_won_BIH_009</t>
   </si>
   <si>
-    <t>wind resource in cluster 9</t>
+    <t>wind onshore resource near Mostar (cluster 9)</t>
   </si>
   <si>
     <t>e_won_BIH_010</t>
   </si>
   <si>
-    <t>wind resource in cluster 10</t>
+    <t>wind onshore resource near Banja Luka (cluster 10)</t>
   </si>
   <si>
     <t>~fi_t: UP</t>
@@ -1207,31 +1207,31 @@
     <t>season</t>
   </si>
   <si>
-    <t>e_Bijeljina_BIH,e_Doboj_BIH,e_Mostar_BIH,e_Prijedor_BIH,e_SirokiBrijeg_BIH,e_Trebinje_BIH,e_Tuzla_BIH</t>
+    <t>e_Bijeljina_BIH,e_Doboj_BIH,e_Mostar_BIH,e_Prijedor_BIH,e_SirokiBrijeg_BIH,e_Trebinje_BIH,e_w841600752-220_BIH</t>
   </si>
   <si>
     <t>region</t>
   </si>
   <si>
-    <t>cement_Tuzla_BIH</t>
+    <t>cement_BA11-220_BIH</t>
   </si>
   <si>
     <t>BIH</t>
   </si>
   <si>
+    <t>capturable co2: cement (1 sites, 382 kt/yr)</t>
+  </si>
+  <si>
+    <t>kt</t>
+  </si>
+  <si>
+    <t>cement_w841600752-220_BIH</t>
+  </si>
+  <si>
     <t>capturable co2: cement (1 sites, 765 kt/yr)</t>
   </si>
   <si>
-    <t>kt</t>
-  </si>
-  <si>
-    <t>cement_Zenica_BIH</t>
-  </si>
-  <si>
-    <t>capturable co2: cement (1 sites, 382 kt/yr)</t>
-  </si>
-  <si>
-    <t>steel_Zenica_BIH</t>
+    <t>steel_BA11-220_BIH</t>
   </si>
   <si>
     <t>capturable co2: steel (1 sites, 2788 kt/yr)</t>
@@ -1255,13 +1255,13 @@
     <t>other_indexes</t>
   </si>
   <si>
-    <t>co2_Tuzla_BIH</t>
+    <t>co2_BA11-220_BIH</t>
   </si>
   <si>
     <t>OUT</t>
   </si>
   <si>
-    <t>co2_Zenica_BIH</t>
+    <t>co2_w841600752-220_BIH</t>
   </si>
   <si>
     <t>co2s_ogci11364_BIH</t>
@@ -6037,7 +6037,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4379985A-6403-4A2E-853D-205680EB2606}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63248EAB-9278-4B54-BCE8-FF90672F2F15}">
   <dimension ref="B9:AP24"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -6233,16 +6233,16 @@
         <v>226</v>
       </c>
       <c r="Y11" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="Z11" t="s">
         <v>258</v>
       </c>
       <c r="AA11">
-        <v>0.99879379702816595</v>
+        <v>0.99889482351948222</v>
       </c>
       <c r="AB11">
-        <v>22.11372115029139</v>
+        <v>20.261568809491827</v>
       </c>
       <c r="AD11" t="s">
         <v>225</v>
@@ -6272,13 +6272,13 @@
         <v>290</v>
       </c>
       <c r="AN11" t="s">
-        <v>259</v>
+        <v>291</v>
       </c>
       <c r="AO11">
-        <v>0.99779158802167667</v>
+        <v>0.9988789069237527</v>
       </c>
       <c r="AP11">
-        <v>40.487552935926864</v>
+        <v>20.553373064533289</v>
       </c>
     </row>
     <row r="12" spans="2:42">
@@ -6343,16 +6343,16 @@
         <v>230</v>
       </c>
       <c r="Y12" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="Z12" t="s">
         <v>259</v>
       </c>
       <c r="AA12">
-        <v>0.99835968962961552</v>
+        <v>0.99895725184677298</v>
       </c>
       <c r="AB12">
-        <v>30.072356790382742</v>
+        <v>19.117049475828384</v>
       </c>
       <c r="AD12" t="s">
         <v>225</v>
@@ -6379,16 +6379,16 @@
         <v>272</v>
       </c>
       <c r="AM12" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AN12" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AO12">
-        <v>0.99818117729588385</v>
+        <v>0.99901634365842085</v>
       </c>
       <c r="AP12">
-        <v>33.345082908796947</v>
+        <v>18.033699595617549</v>
       </c>
     </row>
     <row r="13" spans="2:42">
@@ -6453,16 +6453,16 @@
         <v>232</v>
       </c>
       <c r="Y13" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="Z13" t="s">
         <v>260</v>
       </c>
       <c r="AA13">
-        <v>0.99820230087305606</v>
+        <v>0.99889787806915264</v>
       </c>
       <c r="AB13">
-        <v>32.957817327305797</v>
+        <v>20.205568732201368</v>
       </c>
       <c r="AD13" t="s">
         <v>225</v>
@@ -6489,16 +6489,16 @@
         <v>274</v>
       </c>
       <c r="AM13" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AN13" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AO13">
-        <v>0.99871458436539107</v>
+        <v>0.99710874831259566</v>
       </c>
       <c r="AP13">
-        <v>23.565953301164143</v>
+        <v>53.006280935745359</v>
       </c>
     </row>
     <row r="14" spans="2:42">
@@ -6563,16 +6563,16 @@
         <v>234</v>
       </c>
       <c r="Y14" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="Z14" t="s">
         <v>261</v>
       </c>
       <c r="AA14">
-        <v>0.99800984241308865</v>
+        <v>0.99835968962961552</v>
       </c>
       <c r="AB14">
-        <v>36.486222426708473</v>
+        <v>30.072356790382742</v>
       </c>
       <c r="AD14" t="s">
         <v>225</v>
@@ -6599,16 +6599,16 @@
         <v>276</v>
       </c>
       <c r="AM14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AN14" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO14">
-        <v>0.99762673547698311</v>
+        <v>0.99871458436539107</v>
       </c>
       <c r="AP14">
-        <v>43.509849588643917</v>
+        <v>23.565953301164143</v>
       </c>
     </row>
     <row r="15" spans="2:42">
@@ -6673,16 +6673,16 @@
         <v>236</v>
       </c>
       <c r="Y15" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="Z15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AA15">
-        <v>0.99902947289646282</v>
+        <v>0.99739314616560648</v>
       </c>
       <c r="AB15">
-        <v>17.792996898181659</v>
+        <v>47.792320297215348</v>
       </c>
       <c r="AD15" t="s">
         <v>225</v>
@@ -6709,16 +6709,16 @@
         <v>278</v>
       </c>
       <c r="AM15" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AN15" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="AO15">
-        <v>0.99839442629161379</v>
+        <v>0.99918120906177665</v>
       </c>
       <c r="AP15">
-        <v>29.435517987081209</v>
+        <v>15.011167200760433</v>
       </c>
     </row>
     <row r="16" spans="2:42">
@@ -6783,16 +6783,16 @@
         <v>238</v>
       </c>
       <c r="Y16" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="Z16" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="AA16">
-        <v>0.99739314616560648</v>
+        <v>0.99820230087305606</v>
       </c>
       <c r="AB16">
-        <v>47.792320297215348</v>
+        <v>32.957817327305797</v>
       </c>
       <c r="AD16" t="s">
         <v>225</v>
@@ -6822,13 +6822,13 @@
         <v>299</v>
       </c>
       <c r="AN16" t="s">
-        <v>300</v>
+        <v>261</v>
       </c>
       <c r="AO16">
-        <v>0.99710874831259566</v>
+        <v>0.99688386009726881</v>
       </c>
       <c r="AP16">
-        <v>53.006280935745359</v>
+        <v>57.129231550071403</v>
       </c>
     </row>
     <row r="17" spans="2:42">
@@ -6893,16 +6893,16 @@
         <v>240</v>
       </c>
       <c r="Y17" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="Z17" t="s">
         <v>263</v>
       </c>
       <c r="AA17">
-        <v>0.99712574598898618</v>
+        <v>0.99800984241308865</v>
       </c>
       <c r="AB17">
-        <v>52.69465686858733</v>
+        <v>36.486222426708473</v>
       </c>
       <c r="AD17" t="s">
         <v>225</v>
@@ -6929,16 +6929,16 @@
         <v>282</v>
       </c>
       <c r="AM17" t="s">
+        <v>300</v>
+      </c>
+      <c r="AN17" t="s">
         <v>301</v>
       </c>
-      <c r="AN17" t="s">
-        <v>298</v>
-      </c>
       <c r="AO17">
-        <v>0.99901634365842085</v>
+        <v>0.99818117729588385</v>
       </c>
       <c r="AP17">
-        <v>18.033699595617549</v>
+        <v>33.345082908796947</v>
       </c>
     </row>
     <row r="18" spans="2:42">
@@ -7003,16 +7003,16 @@
         <v>242</v>
       </c>
       <c r="Y18" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Z18" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="AA18">
-        <v>0.99824014200820133</v>
+        <v>0.99869492385700986</v>
       </c>
       <c r="AB18">
-        <v>32.264063182976258</v>
+        <v>23.926395954819476</v>
       </c>
       <c r="AD18" t="s">
         <v>225</v>
@@ -7042,13 +7042,13 @@
         <v>302</v>
       </c>
       <c r="AN18" t="s">
-        <v>303</v>
+        <v>261</v>
       </c>
       <c r="AO18">
-        <v>0.9988789069237527</v>
+        <v>0.99779158802167667</v>
       </c>
       <c r="AP18">
-        <v>20.553373064533289</v>
+        <v>40.487552935926864</v>
       </c>
     </row>
     <row r="19" spans="2:42">
@@ -7113,16 +7113,16 @@
         <v>244</v>
       </c>
       <c r="Y19" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Z19" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="AA19">
-        <v>0.99869492385700986</v>
+        <v>0.9974725186889053</v>
       </c>
       <c r="AB19">
-        <v>23.926395954819476</v>
+        <v>46.337157370070273</v>
       </c>
       <c r="AD19" t="s">
         <v>225</v>
@@ -7149,16 +7149,16 @@
         <v>286</v>
       </c>
       <c r="AM19" t="s">
+        <v>303</v>
+      </c>
+      <c r="AN19" t="s">
         <v>304</v>
       </c>
-      <c r="AN19" t="s">
-        <v>259</v>
-      </c>
       <c r="AO19">
-        <v>0.99688386009726881</v>
+        <v>0.99762673547698311</v>
       </c>
       <c r="AP19">
-        <v>57.129231550071403</v>
+        <v>43.509849588643917</v>
       </c>
     </row>
     <row r="20" spans="2:42">
@@ -7223,16 +7223,16 @@
         <v>246</v>
       </c>
       <c r="Y20" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="Z20" t="s">
         <v>265</v>
       </c>
       <c r="AA20">
-        <v>0.9974725186889053</v>
+        <v>0.99829247407956323</v>
       </c>
       <c r="AB20">
-        <v>46.337157370070273</v>
+        <v>31.304641874674619</v>
       </c>
       <c r="AD20" t="s">
         <v>225</v>
@@ -7262,13 +7262,13 @@
         <v>305</v>
       </c>
       <c r="AN20" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="AO20">
-        <v>0.99918120906177665</v>
+        <v>0.99839442629161379</v>
       </c>
       <c r="AP20">
-        <v>15.011167200760433</v>
+        <v>29.435517987081209</v>
       </c>
     </row>
     <row r="21" spans="2:42">
@@ -7333,16 +7333,16 @@
         <v>248</v>
       </c>
       <c r="Y21" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="Z21" t="s">
         <v>266</v>
       </c>
       <c r="AA21">
-        <v>0.99829247407956323</v>
+        <v>0.99879379702816595</v>
       </c>
       <c r="AB21">
-        <v>31.304641874674619</v>
+        <v>22.11372115029139</v>
       </c>
     </row>
     <row r="22" spans="2:42">
@@ -7407,16 +7407,16 @@
         <v>250</v>
       </c>
       <c r="Y22" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="Z22" t="s">
         <v>267</v>
       </c>
       <c r="AA22">
-        <v>0.99889482351948222</v>
+        <v>0.99712574598898618</v>
       </c>
       <c r="AB22">
-        <v>20.261568809491827</v>
+        <v>52.69465686858733</v>
       </c>
     </row>
     <row r="23" spans="2:42">
@@ -7481,16 +7481,16 @@
         <v>252</v>
       </c>
       <c r="Y23" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="Z23" t="s">
         <v>268</v>
       </c>
       <c r="AA23">
-        <v>0.99895725184677298</v>
+        <v>0.99824014200820133</v>
       </c>
       <c r="AB23">
-        <v>19.117049475828384</v>
+        <v>32.264063182976258</v>
       </c>
     </row>
     <row r="24" spans="2:42">
@@ -7555,16 +7555,16 @@
         <v>254</v>
       </c>
       <c r="Y24" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Z24" t="s">
         <v>269</v>
       </c>
       <c r="AA24">
-        <v>0.99889787806915264</v>
+        <v>0.99902947289646282</v>
       </c>
       <c r="AB24">
-        <v>20.205568732201368</v>
+        <v>17.792996898181659</v>
       </c>
     </row>
   </sheetData>
@@ -7573,7 +7573,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31B6A585-1B87-434B-BBFC-2908B7B8427F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57409622-AE23-4DC4-9A40-375525992EC7}">
   <dimension ref="B9:M20"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7646,7 +7646,7 @@
         <v>306</v>
       </c>
       <c r="K11" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="L11">
         <v>0.56863785226837649</v>
@@ -7681,7 +7681,7 @@
         <v>308</v>
       </c>
       <c r="K12" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="L12">
         <v>0.23116039134301808</v>
@@ -7716,7 +7716,7 @@
         <v>310</v>
       </c>
       <c r="K13" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="L13">
         <v>0.39159952195983067</v>
@@ -7751,7 +7751,7 @@
         <v>312</v>
       </c>
       <c r="K14" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="L14">
         <v>3.0763380697294368E-2</v>
@@ -7786,7 +7786,7 @@
         <v>314</v>
       </c>
       <c r="K15" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="L15">
         <v>3.5282392026578066E-3</v>
@@ -7821,7 +7821,7 @@
         <v>316</v>
       </c>
       <c r="K16" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="L16">
         <v>2.1425014560279561E-2</v>
@@ -7856,7 +7856,7 @@
         <v>318</v>
       </c>
       <c r="K17" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="L17">
         <v>4.5486319112766124E-3</v>
@@ -7891,7 +7891,7 @@
         <v>320</v>
       </c>
       <c r="K18" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="L18">
         <v>2.0912315029962093E-2</v>
@@ -7926,7 +7926,7 @@
         <v>322</v>
       </c>
       <c r="K19" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="L19">
         <v>0.78795980699251933</v>
@@ -7961,7 +7961,7 @@
         <v>324</v>
       </c>
       <c r="K20" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="L20">
         <v>0.1943077875619153</v>
@@ -7976,7 +7976,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C6766BD-D351-4174-82EB-DBA3074A7F07}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8AC791B-40C6-4BB6-AB4C-F870AAEE243E}">
   <dimension ref="B9:U116"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -11460,7 +11460,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5732787D-763E-430F-9935-6F808B1210BF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58DE817B-344F-4CEF-B7DF-BA7000A44F3F}">
   <dimension ref="B9:T14"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -11563,7 +11563,7 @@
         <v>375</v>
       </c>
       <c r="N11">
-        <v>765</v>
+        <v>382.5</v>
       </c>
       <c r="O11">
         <v>50</v>
@@ -11616,7 +11616,7 @@
         <v>377</v>
       </c>
       <c r="N12">
-        <v>382.5</v>
+        <v>765</v>
       </c>
       <c r="O12">
         <v>50</v>
@@ -11666,7 +11666,7 @@
         <v>362</v>
       </c>
       <c r="M13" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="N13">
         <v>2788</v>
